--- a/data/export/2026-10-26-182路.xlsx
+++ b/data/export/2026-10-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,17 +812,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -820,13 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -887,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -937,7 +953,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -998,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1053,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1048,7 +1064,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1092,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1109,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,17 +1153,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1153,13 +1173,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1294,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1405,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1516,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1500,22 +1524,22 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1548,12 +1572,12 @@
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1567,7 +1591,7 @@
       <c r="T10" s="2" t="inlineStr"/>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1603,7 +1627,788 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>1/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A32899D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-182路.xlsx
+++ b/data/export/2026-10-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>77.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -870,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -903,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -927,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -947,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1064,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1102,24 +1110,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1129,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1168,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1211,32 +1219,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1244,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1268,33 +1280,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1322,32 +1338,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1355,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1379,33 +1399,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1433,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -1466,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1490,33 +1518,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1627,7 +1659,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1738,7 +1770,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1849,7 +1881,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1942,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1964,7 +1996,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2057,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2075,7 +2107,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2168,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2186,7 +2218,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2279,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2291,13 +2323,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2305,22 +2341,22 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2358,7 +2394,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2372,43 +2408,729 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr"/>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>—/13</t>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-182路.xlsx
+++ b/data/export/2026-10-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1348,24 +1348,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1467,24 +1467,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1687,32 +1687,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1720,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1744,33 +1748,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1942,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2057,7 +2065,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2168,7 +2176,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2279,7 +2287,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2394,7 +2402,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2509,7 +2517,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2620,7 +2628,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2735,7 +2743,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,7 +2854,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,7 +2969,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3010,7 +3018,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3076,7 +3084,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3125,12 +3133,238 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-182路.xlsx
+++ b/data/export/2026-10-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1576,32 +1576,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -1609,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1633,17 +1637,17 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1653,13 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1705,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1724,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1773,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1806,32 +1814,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1839,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1863,33 +1875,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1917,32 +1933,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1950,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1974,37 +1994,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2032,32 +2052,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2065,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2089,33 +2113,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2143,32 +2171,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -2176,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2200,33 +2232,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2254,32 +2290,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2287,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2311,37 +2351,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2456,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2556,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2628,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2682,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2854,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2908,7 +2948,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2969,7 +3009,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,7 +3239,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3243,13 +3283,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3359,12 +3403,698 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A32899D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
           <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-182路.xlsx
+++ b/data/export/2026-10-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,13 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,14 +1180,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>89.0</t>
@@ -1191,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,17 +1775,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1851,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,17 +2018,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,7 +2132,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2143,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2262,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2385,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2524,32 +2528,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2557,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2581,17 +2589,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2601,13 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2635,32 +2647,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2668,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2692,29 +2708,29 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>89.0</t>
@@ -2722,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,7 +2838,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2861,32 +2877,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -2894,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2918,37 +2938,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2976,32 +2996,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3009,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3033,37 +3057,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3091,32 +3115,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -3124,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3148,17 +3176,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3168,17 +3196,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3206,32 +3234,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -3239,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3263,37 +3295,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3321,32 +3353,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3354,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3378,32 +3414,32 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3436,32 +3472,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3469,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3493,17 +3533,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3513,17 +3553,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3551,32 +3591,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3584,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3608,17 +3652,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3628,17 +3672,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3738,7 +3782,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3753,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3868,7 +3912,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3983,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3991,22 +4035,22 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4044,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4058,43 +4102,963 @@
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y31" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z31" s="2" t="inlineStr">
+      <c r="Z32" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr"/>
-      <c r="AC31" s="2" t="inlineStr">
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
         <is>
           <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A32899D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-182路.xlsx
+++ b/data/export/2026-10-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,17 +1299,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,14 +2013,14 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,22 +2251,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,22 +2370,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,22 +2604,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,17 +2953,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3482,24 +3482,24 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3667,14 +3667,14 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3710,32 +3710,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -3743,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3767,17 +3771,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3787,17 +3791,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3825,32 +3829,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -3858,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3882,37 +3890,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3940,32 +3948,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3973,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3997,37 +4009,37 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4055,32 +4067,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4088,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4112,17 +4128,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4132,12 +4148,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4170,32 +4186,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4203,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4227,37 +4247,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4285,32 +4305,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4318,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4342,17 +4366,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4362,12 +4386,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4433,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4472,7 +4496,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4511,32 +4535,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -4544,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4568,32 +4596,32 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4659,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4713,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4828,7 +4856,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4943,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4951,22 +4979,22 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A32899D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4999,12 +5027,12 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5018,47 +5046,733 @@
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr">
         <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A32899D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X39" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
+      <c r="Z40" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>13/14</t>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>84.3</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>82.7</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-182路.xlsx
+++ b/data/export/2026-10-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC45"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,14 +1894,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>87.5</t>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2018,17 +2018,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2843,13 +2843,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2963,12 +2967,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3077,12 +3081,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3206,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,22 +3314,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3434,12 +3438,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3509,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3548,14 +3552,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>87.5</t>
@@ -3563,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3672,17 +3676,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3786,22 +3790,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,7 +3909,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3920,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4039,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,7 +4147,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4223,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4277,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4315,24 +4319,24 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4342,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,22 +4385,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4424,32 +4428,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -4457,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4481,17 +4489,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4501,13 +4509,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4545,24 +4557,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4572,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,12 +4633,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4654,32 +4666,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4687,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4711,17 +4727,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4731,12 +4747,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4769,32 +4785,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -4802,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4826,37 +4846,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4884,32 +4904,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4917,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4941,17 +4965,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4961,12 +4985,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -4999,32 +5023,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5032,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5056,17 +5084,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5076,17 +5104,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5114,32 +5142,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -5147,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5171,37 +5203,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5316,7 +5348,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5416,7 +5448,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5431,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5546,7 +5578,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5651,13 +5683,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5767,12 +5803,702 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A32899D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
           <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-182路.xlsx
+++ b/data/export/2026-10-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,14 +1418,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>80.7</t>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,14 +1775,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>86.0</t>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,17 +2256,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2375,17 +2375,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,22 +2838,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2962,17 +2962,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,14 +3076,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>80.7</t>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,14 +3433,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>86.0</t>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,22 +3552,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3914,17 +3914,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4033,17 +4033,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4504,22 +4504,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4628,17 +4628,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,14 +4742,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>80.7</t>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4980,14 +4980,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>86.0</t>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -5033,24 +5033,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5261,32 +5261,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5294,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5318,17 +5322,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5338,17 +5342,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5376,32 +5380,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -5409,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5433,17 +5441,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5453,17 +5461,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5491,32 +5499,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5524,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5548,17 +5560,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5568,17 +5580,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5606,32 +5618,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -5639,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5663,37 +5679,37 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -5721,32 +5737,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -5754,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5778,17 +5798,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5798,17 +5818,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5951,32 +5971,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5984,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6008,37 +6032,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6153,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6329,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6373,17 +6397,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6498,7 +6522,467 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-182路.xlsx
+++ b/data/export/2026-10-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,14 +1537,14 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>81.5</t>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,17 +2485,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,14 +3195,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>81.5</t>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3795,17 +3795,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4147,17 +4147,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5856,32 +5856,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -5889,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5913,17 +5917,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5933,12 +5937,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5981,24 +5985,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6008,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6057,12 +6061,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6090,32 +6094,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -6123,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6147,17 +6155,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6167,17 +6175,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6205,32 +6213,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6238,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6262,32 +6274,32 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6353,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6468,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6507,7 +6519,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6583,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6637,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6813,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6862,12 +6874,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6986,6 +6998,466 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>79.8</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-26-182路.xlsx
+++ b/data/export/2026-10-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,17 +2256,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3914,17 +3914,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4390,17 +4390,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4509,17 +4509,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5461,17 +5461,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5699,17 +5699,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6223,24 +6223,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6332,32 +6332,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -6365,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6389,17 +6393,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6409,17 +6413,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6447,32 +6451,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6480,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6504,17 +6512,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6524,17 +6532,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6562,32 +6570,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -6595,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6619,17 +6631,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6639,17 +6651,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6749,7 +6761,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6825,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6879,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7055,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7104,12 +7116,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7285,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7400,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7444,17 +7456,247 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB59" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>13/14</t>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-182路.xlsx
+++ b/data/export/2026-10-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,14 +1299,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,14 +1656,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>78.2</t>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,17 +1775,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,22 +2013,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,14 +2957,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,14 +3314,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>78.2</t>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,17 +3433,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3557,17 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,22 +3671,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4152,12 +4152,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,14 +4623,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4861,14 +4861,14 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>78.2</t>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4980,17 +4980,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5099,22 +5099,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5813,14 +5813,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5932,14 +5932,14 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>78.2</t>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6056,17 +6056,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6354,12 +6354,12 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6461,24 +6461,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6537,12 +6537,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6580,24 +6580,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6689,32 +6689,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6722,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6746,17 +6750,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6766,12 +6770,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6804,32 +6808,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6837,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6861,17 +6869,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6881,17 +6889,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6919,32 +6927,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6952,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6976,32 +6988,32 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7034,32 +7046,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7067,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7091,17 +7107,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7111,12 +7127,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7149,32 +7165,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7182,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7206,37 +7226,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7336,7 +7356,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7351,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7461,12 +7481,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7642,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7686,17 +7706,707 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>80.7</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>7/14</t>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-182路.xlsx
+++ b/data/export/2026-10-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,14 +1894,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,14 +2132,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>80.8</t>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,17 +2370,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,22 +2957,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,14 +3790,14 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>80.8</t>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,17 +4028,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4390,17 +4390,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,22 +4623,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,14 +5218,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>80.8</t>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5813,22 +5813,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6051,14 +6051,14 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,14 +6170,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>80.8</t>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6532,17 +6532,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6770,17 +6770,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6884,14 +6884,14 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6937,24 +6937,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7175,24 +7175,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7284,32 +7284,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -7317,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7341,17 +7345,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7361,17 +7365,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7399,32 +7403,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7432,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7456,17 +7464,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7476,17 +7484,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7514,32 +7522,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7547,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7571,32 +7583,32 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7629,32 +7641,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7662,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7686,17 +7702,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7706,17 +7722,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7744,32 +7760,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -7777,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7801,37 +7821,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7941,7 +7961,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8007,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8046,7 +8066,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8061,7 +8081,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8176,7 +8196,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8286,12 +8306,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8299,22 +8319,22 @@
       <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>沪A12050A</t>
+          <t>沪A32899D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8347,12 +8367,12 @@
       <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8366,47 +8386,852 @@
       <c r="T67" s="2" t="inlineStr"/>
       <c r="U67" s="2" t="inlineStr">
         <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
           <t>16:20</t>
         </is>
       </c>
-      <c r="V67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W67" s="2" t="inlineStr">
+      <c r="W68" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X67" s="2" t="inlineStr">
+      <c r="X68" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y67" s="2" t="inlineStr">
+      <c r="Y68" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z67" s="2" t="inlineStr">
+      <c r="Z68" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>81.5</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr">
-        <is>
-          <t>11/14</t>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-182路.xlsx
+++ b/data/export/2026-10-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,14 +1180,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>80.4</t>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,17 +1775,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,17 +1894,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,22 +2013,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,14 +2723,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>80.4</t>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,22 +3076,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,17 +3433,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,17 +3552,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,22 +3671,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4385,14 +4385,14 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
           <t>80.4</t>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,22 +4742,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4861,22 +4861,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4980,17 +4980,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5099,22 +5099,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5932,22 +5932,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6051,17 +6051,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,14 +6527,14 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
           <t>80.4</t>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6765,22 +6765,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6884,17 +6884,17 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7003,17 +7003,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7241,22 +7241,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7365,17 +7365,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,14 +7479,14 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>80.4</t>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7651,24 +7651,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7717,22 +7717,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7782,12 +7782,12 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7879,32 +7879,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7912,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7936,32 +7940,32 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7994,32 +7998,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8027,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8051,17 +8059,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8071,12 +8079,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8109,32 +8117,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -8142,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8166,37 +8178,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8224,32 +8236,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8257,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8281,37 +8297,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8411,7 +8427,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8426,7 +8442,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8454,32 +8470,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -8487,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8511,17 +8531,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8531,17 +8551,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8569,32 +8589,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8602,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8626,32 +8650,32 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8717,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8832,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8886,7 +8910,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9062,7 +9086,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9116,7 +9140,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9124,22 +9148,22 @@
       <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9177,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9191,47 +9215,967 @@
       <c r="T74" s="2" t="inlineStr"/>
       <c r="U74" s="2" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>80.4</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="V74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W74" s="2" t="inlineStr">
+      <c r="W75" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X74" s="2" t="inlineStr">
+      <c r="X75" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y74" s="2" t="inlineStr">
+      <c r="Y75" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z74" s="2" t="inlineStr">
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB74" s="2" t="inlineStr">
-        <is>
-          <t>77.3</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
         <is>
           <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>79.4</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A32899D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>83.2</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-182路.xlsx
+++ b/data/export/2026-10-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,22 +2251,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,17 +2370,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,22 +2485,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,22 +2838,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,22 +2957,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,22 +3909,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,17 +4028,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4385,22 +4385,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4504,22 +4504,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,22 +4623,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5456,22 +5456,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5580,17 +5580,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5694,22 +5694,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5813,22 +5813,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6289,22 +6289,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6408,22 +6408,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,22 +6527,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,22 +6646,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7122,22 +7122,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,22 +7479,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7598,17 +7598,17 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7836,22 +7836,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8079,17 +8079,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8355,32 +8355,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -8388,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8412,17 +8416,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8432,12 +8436,12 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8480,12 +8484,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -8507,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8556,12 +8560,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8599,24 +8603,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8626,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8675,7 +8679,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8708,32 +8712,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8741,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8765,37 +8773,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8823,32 +8831,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8856,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8880,32 +8892,32 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8938,32 +8950,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -8971,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8995,37 +9011,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -9053,32 +9069,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -9086,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9110,37 +9130,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -9168,32 +9188,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9201,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9225,37 +9249,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9283,32 +9307,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -9316,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9340,37 +9368,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9398,32 +9426,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9431,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9455,17 +9487,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9475,17 +9507,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9600,7 +9632,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9700,7 +9732,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9715,7 +9747,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9820,12 +9852,12 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9891,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9945,7 +9977,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -10006,7 +10038,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10055,7 +10087,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10068,22 +10100,22 @@
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10121,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10165,17 +10197,822 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>78.6</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
+      <c r="AB83" s="2" t="inlineStr">
         <is>
           <t>77.7</t>
         </is>
       </c>
-      <c r="AC82" s="2" t="inlineStr">
-        <is>
-          <t>6/14</t>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>75.4</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-182路.xlsx
+++ b/data/export/2026-10-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,17 +1418,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,17 +1775,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,17 +2013,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,17 +3433,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3557,12 +3557,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,17 +4742,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4980,17 +4980,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5099,17 +5099,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,22 +5218,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,22 +6170,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6765,17 +6765,17 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7003,17 +7003,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7241,17 +7241,17 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7717,17 +7717,17 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7955,17 +7955,17 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8312,17 +8312,17 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8431,22 +8431,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9317,24 +9317,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9436,12 +9436,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9545,32 +9545,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9578,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9602,32 +9606,32 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9693,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9747,7 +9751,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9779,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -9808,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9832,37 +9840,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9890,32 +9898,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9923,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9947,32 +9959,32 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10005,32 +10017,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10038,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10062,17 +10078,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10082,12 +10098,12 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10153,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10235,32 +10251,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10268,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10292,32 +10312,32 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10383,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10498,7 +10518,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10613,7 +10633,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10667,7 +10687,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10728,7 +10748,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10777,7 +10797,7 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10843,7 +10863,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10892,7 +10912,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10905,22 +10925,22 @@
       <c r="A89" s="2" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>沪A55712D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -10953,12 +10973,12 @@
       <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10972,47 +10992,507 @@
       <c r="T89" s="2" t="inlineStr"/>
       <c r="U89" s="2" t="inlineStr">
         <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="V89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W89" s="2" t="inlineStr">
+      <c r="W90" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X89" s="2" t="inlineStr">
+      <c r="X90" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y89" s="2" t="inlineStr">
+      <c r="Y90" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z89" s="2" t="inlineStr">
+      <c r="Z90" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA89" s="2" t="inlineStr">
+      <c r="AA90" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB89" s="2" t="inlineStr">
+      <c r="AB90" s="2" t="inlineStr">
         <is>
           <t>76.0</t>
         </is>
       </c>
-      <c r="AC89" s="2" t="inlineStr">
-        <is>
-          <t>2/14</t>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A32899D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-182路.xlsx
+++ b/data/export/2026-10-26-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC93"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,17 +2256,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,22 +2370,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,22 +2957,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3914,17 +3914,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,22 +4028,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4390,17 +4390,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4509,17 +4509,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,22 +4623,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4861,22 +4861,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,22 +5337,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5461,17 +5461,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5699,17 +5699,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5813,22 +5813,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5932,22 +5932,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6294,17 +6294,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6413,17 +6413,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6532,17 +6532,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6651,17 +6651,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6770,17 +6770,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7127,17 +7127,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7484,17 +7484,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7598,22 +7598,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7722,17 +7722,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7836,22 +7836,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8193,22 +8193,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8793,17 +8793,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8907,22 +8907,22 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9031,17 +9031,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9145,22 +9145,22 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9269,17 +9269,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9388,17 +9388,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9626,17 +9626,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9736,22 +9736,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10027,24 +10027,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -10136,32 +10136,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10169,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10193,17 +10197,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10213,17 +10217,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10261,24 +10265,24 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10288,7 +10292,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10337,7 +10341,7 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10370,32 +10374,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -10403,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10427,17 +10435,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10447,17 +10455,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10485,32 +10493,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10518,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10542,37 +10554,37 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA85" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10600,32 +10612,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10633,7 +10649,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10657,17 +10673,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10677,17 +10693,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -10715,32 +10731,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -10748,7 +10768,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10772,17 +10792,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10792,17 +10812,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10830,32 +10850,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -10863,7 +10887,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10887,37 +10911,37 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA88" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10945,32 +10969,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10978,7 +11006,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11002,17 +11030,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11022,17 +11050,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -11060,32 +11088,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -11093,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11117,37 +11149,37 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -11208,7 +11240,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11262,7 +11294,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -11323,7 +11355,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11372,7 +11404,7 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11438,7 +11470,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11477,22 +11509,482 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA93" s="2" t="inlineStr">
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>79.4</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB93" s="2" t="inlineStr">
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A32899D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
         <is>
           <t>82.5</t>
         </is>
       </c>
-      <c r="AC93" s="2" t="inlineStr">
-        <is>
-          <t>11/14</t>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-182路.xlsx
+++ b/data/export/2026-10-26-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3438,17 +3438,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3795,17 +3795,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4985,17 +4985,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6175,17 +6175,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7008,17 +7008,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7960,17 +7960,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8436,17 +8436,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9860,17 +9860,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9979,17 +9979,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -11110,12 +11110,12 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11207,32 +11207,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11240,7 +11244,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11264,17 +11268,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11284,17 +11288,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -11322,32 +11326,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11355,7 +11363,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11379,17 +11387,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11399,12 +11407,12 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11437,32 +11445,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11470,7 +11482,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11494,17 +11506,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11514,17 +11526,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11585,7 +11597,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11700,7 +11712,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11754,7 +11766,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -11815,7 +11827,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11930,7 +11942,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11974,17 +11986,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-182路.xlsx
+++ b/data/export/2026-10-26-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2375,17 +2375,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4033,17 +4033,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5342,17 +5342,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7603,17 +7603,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8912,17 +8912,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10574,17 +10574,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11336,12 +11336,12 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
@@ -11363,7 +11363,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11412,7 +11412,7 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11455,24 +11455,24 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11564,32 +11564,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11597,7 +11601,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11621,17 +11625,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11641,17 +11645,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -11679,32 +11683,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -11712,7 +11720,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11736,17 +11744,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11756,12 +11764,12 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11827,7 +11835,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11942,7 +11950,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11991,7 +11999,7 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
